--- a/survey_templates/050_surgical_precision_evaluation_survey--survey_templates.xlsx
+++ b/survey_templates/050_surgical_precision_evaluation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1352,8 +1352,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'surgical_procedure_1'}</t>
+          <t>surgical_procedure_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Surgical procedure 1'}</t>
+          <t>Surgical procedure 1</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'surgical_procedure_2'}</t>
+          <t>surgical_procedure_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Surgical procedure 2'}</t>
+          <t>Surgical procedure 2</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'surgical_procedure_3'}</t>
+          <t>surgical_procedure_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Surgical procedure 3'}</t>
+          <t>Surgical procedure 3</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
